--- a/Result/profitability/1213.xlsx
+++ b/Result/profitability/1213.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9912500000000001</v>
+        <v>1.00875</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.279999999999996</v>
+        <v>-2.994999999999997</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0325</v>
+        <v>-0.1725</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.194999999999996</v>
+        <v>1.765000000000003</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1387499999999999</v>
+        <v>-0.1325</v>
       </c>
       <c r="N4" t="n">
-        <v>3.958750000000004</v>
+        <v>4.583750000000004</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1112499999999999</v>
+        <v>-0.105</v>
       </c>
       <c r="N5" t="n">
-        <v>6.256250000000003</v>
+        <v>6.082500000000003</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07249999999999988</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>8.313750000000002</v>
+        <v>8.173750000000004</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.09749999999999989</v>
+        <v>-0.095</v>
       </c>
       <c r="N7" t="n">
-        <v>10.1425</v>
+        <v>10.41</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.3</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0349999999999999</v>
+        <v>-0.01125</v>
       </c>
       <c r="N8" t="n">
-        <v>12.69625</v>
+        <v>12.75375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04250000000000011</v>
+        <v>0.0425</v>
       </c>
       <c r="N9" t="n">
         <v>14.04</v>
@@ -1645,7 +1645,7 @@
         <v>0.08</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05000000000000011</v>
+        <v>0.05</v>
       </c>
       <c r="N10" t="n">
         <v>13.91125</v>
@@ -1772,7 +1772,7 @@
         <v>-0.44</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.006249999999999895</v>
+        <v>-0.006250000000000006</v>
       </c>
       <c r="N11" t="n">
         <v>13.46625</v>
@@ -1899,7 +1899,7 @@
         <v>0.05</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01124999999999989</v>
+        <v>-0.01125</v>
       </c>
       <c r="N12" t="n">
         <v>12.8275</v>
@@ -2026,7 +2026,7 @@
         <v>0.03</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.006249999999999891</v>
+        <v>-0.006250000000000002</v>
       </c>
       <c r="N13" t="n">
         <v>13.11</v>
@@ -9804,6 +9804,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>74</v>
+      </c>
+      <c r="D75" t="n">
+        <v>75</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9662500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-5.421249999999996</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5135135135135136</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.05000000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2173913043478262</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>9.266666666666667</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
